--- a/TESTS/zlit_7_mify.xlsx
+++ b/TESTS/zlit_7_mify.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Міф про походження і народження богів — наприклад «Теогонія» Гесіода описує генеалогію олімпійських богів</t>
+          <t>Міф про походження і народження богів</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Міф що пояснює виникнення світу — як виник космос із хаосу чи безоднічності</t>
+          <t>Міф що пояснює виникнення світу</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Гора де жили дванадцять олімпійських богів — центр божественної влади</t>
+          <t>Гора де жили дванадцять олімпійських богів</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Покоління богів що передувало олімпійцям — Кронос повалив батька Урана а потім сам був повалений Зевсом</t>
+          <t>Покоління богів що передувало олімпійцям</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Бо пророцтво сказало що один з його дітей повалить його — він намагався запобігти цьому</t>
+          <t>Бо пророцтво сказало що один з його дітей повалить його</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Рея підсунула Кроносу загорнутий камінь замість Зевса — зрілий Зевс примусив батька виригнути всіх поглинених</t>
+          <t>Рея підсунула Кроносу загорнутий камінь замість Зевса</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Зевс — небо і земля Посейдон — море Аїд — підземне царство мертвих</t>
+          <t>Зевс</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -897,6 +937,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -939,6 +984,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Хто з олімпійських богів відповідав за сонце і музику?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Зевс</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Аполлон — бог сонця, мистецтв, пророцтва і цілительства</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Арес</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Гермес</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Яке пояснення зміни пір року давали давньогрецькі mythи?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бог сонця втомлювався</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Персефона — донька богині родючості Деметри — на частину року мусила жити в підземному царстві Аїда</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Зевс посилав холод</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Атлант нахиляв землю</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Хто такий Посейдон і з якими природними явищами його пов'язували?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бог неба</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бог морів, що міг викликати землетруси, вдаряючи тризубом</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бог підземного царства</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бог вогню</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Хто такий Аргонавти і чого вони шукали?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Грецькі жерці</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Герої на чолі з Ясоном, що відправились на кораблі «Арго» за Золотим Руном</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Боги Олімпу</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Троянські воїни</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Що таке «Золоте Руно»?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Золота монета</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Шерсть чарівного барана — символ влади і щастя, що зберігалась у Колхіді</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Золотий скіпетр</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нагорода за подвиг на олімпійських іграх</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Хто з жінок допоміг Ясону здобути Золоте Руно в Колхіді?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Афіна</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Чарівниця Медея, що закохалась у нього і зрадила власного батька</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Гера</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Афродіта</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Хто такий Орфей і яким талантом він славився?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Герой-воїн</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Чудовий ліричний поет і музикант, чия лра і спів зачаровували людей, тварин і навіть каміння</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бог мистецтв</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Титан-велет</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Навіщо Орфей спустився у підземне царство Аїда?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>За золотом</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Щоб повернути свою дружину Еврідіку, укушену змією і мертву</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Щоб перемогти смерть заради слави</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Щоб вкрасти секрет безсмертя</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Яку умову поставив Аїд Орфею для повернення Еврідіки?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Перемогти в поєдинку</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Іти вперед і не озиратись на Еврідіку до виходу з підземного царства</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Принести жертву</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Залишитись навік</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Чому Орфей порушив умову і озирнувся?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він забув умову</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Не витримав сумніву і страху — раптово підозрівши, чи Еврідіка справді іде за ним</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Його штовхнули</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Аїд обдурив його</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Що таке «катабазис» у контексті давньогрецьких мифів?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Жертвоприношення</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Спуск живого героя у підземне царство і повернення назад — символ подолання смерті</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Битва з чудовиськом</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Подорож на море</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Яку ідею несе трагедія Орфея — не зміг стримати погляду?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Що любов нічого не варта</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Навіть найсильніша любов і найбільший талант не можуть перемогти смерть без стриманості і довіри</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Що Аїд завжди обманює</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Що музика безсила</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Що таке «гібрис» (hybris) у давньогрецькому розумінні?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Фізична сила</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Надмірна пиха і зарозумілість, що веде людину або героя до руйнівних наслідків</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Мудрість богів</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Форма молитви</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Яким прикладом гібрису є міф про Ніобу?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вона вкрала у богів вогонь</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона хвалилась, що її діти кращі за дітей богині Лето — і боги покарали її жорстоко</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона ухилилась від служби богам</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона не приносила жертв</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Як тема гібрису пов'язана з образом Ікара, якого вивчали у 6 класі?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ікар не мав гібрису</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ікар пережив класичний гібрис — знехтував попередженням батька і злетів занадто близько до сонця</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Гібрис стосується лише богів</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ікар і Ніоба — різні теми без зв'язку</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Що таке «архетип» у контексті mythологічних образів, за Юнгом?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Перший відомий міф</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Первинний образ або модель поведінки, що повторюється в mythах різних народів: герой, мудрець, трікстер</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Найстаріший храм</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Специфічно грецький символ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Наведи приклад mythологічного архетипу «трікстера» у давньогрецьких mythах.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Геракл</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Гермес, що обдурює богів, краде худобу у Аполлона як немовля і виходить сухим з води</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Зевс</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Аїд</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Як давньогрецькі mythи пояснюють щоденний рух сонця?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Зевс щодня піднімає сонце</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Аполлон щодня проїжджає небом на золотій колісниці, запряженій вогняними кіньми</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Прометей несе сонце</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Геракл кидає сонце</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Яким прикладом у сучасній мові ілюструється поняття гібрис?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Скромність перед успіхом</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Людина, що хвалиться і перебільшує власні досягнення до тих пір, поки не зазнає болісного падіння</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Відповідальність лідера</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Відданість другу</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Що таке «трагічна вина» героя у давньогрецьких mythах?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Злочин проти закону</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Внутрішня риса або помилка, що неминуче призводить до загибелі, навіть якщо герой добрий загалом</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Зрада богів</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Жорстокість до людей</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Яке значення мають давньогрецькі mythи для сучасної людини 7 класу?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лише історичне</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони пояснюють вічні людські питання: межі гордості, силу мистецтва, відплату за свавілля і ціну кохання</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони нецікаві сучасним</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони важливі лише для греків</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Як давньогрецькі mythи пояснюють природні явища?</t>
+          <t>Давньогрецькі mythи пояснюють природні явища через образи богів і героїв: сонце — Аполлон, землетруси — Посейдон, зміна пір року — Персефона.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яке значення давньогрецьких mythів для сучасної культури?</t>
+          <t>Давньогрецька mythологія є фундаментом західноєвропейської літератури, мистецтва і навіть наукової термінології.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Що таке «архетип» у контексті mythологічних образів?</t>
+          <t>«Архетип» у mythології — це унікальний образ, що існує лише в одній культурі і не зустрічається в mythах інших народів.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Що таке «катабазис» як мотив давньогрецьких mythів?</t>
+          <t>«Катабазис» — мотив спуску живого героя у підземне царство, що символізує зустріч зі смертю і повернення до życia.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яка трагедія Орфея і яку ідею вона несе?</t>
+          <t>Трагедія Орфея полягає в тому, що він порушив умову Аїда і озирнувся, втративши Еврідіку назавжди.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Що таке «hybris» (гібрис) і яких персонажів він знищив?</t>
+          <t>Гібрис (hybris) — це чеснота, яку боги нагороджують у давньогрецьких mythах.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які давньогрецькі mythи пояснюють природні явища?</t>
+          <t>Які теми є центральними у давньогрецьких mythах 7 класу?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Myth про Аполлона (рух сонця)</t>
+          <t>Трагедія Орфея через порушення умови</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Myth про Персефону (зміна пір року)</t>
+          <t>Гібрис як причина падіння героїв</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Myth про будівництво храмів</t>
+          <t>Аргонавти успішно уникли всіх небезпек</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Myth про Посейдона (землетруси)</t>
+          <t>Катабазис як зустріч зі смертю</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Гібрис — надмірна гордість що призводить до загибелі; боги карають тих хто зрівнюється з ними</t>
+          <t>Гібрис</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Боротьбу з багатоголовим злом — відрубуєш голову виростає дві; перемога можлива лише через мудрість і допомогу</t>
+          <t>Боротьбу з багатоголовим злом</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Шерсть чарівного барана символ влади і багатства — за ним вирушали аргонавти на чолі з Язоном</t>
+          <t>Шерсть чарівного барана символ влади і багатства</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
